--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 65 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2424,8 +2424,8 @@
       <c r="R17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>1</v>
+      <c r="S17" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T17" s="10" t="n">
         <v>1</v>
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5704,8 +5704,8 @@
       <c r="V49" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W49" s="9" t="n">
-        <v>3</v>
+      <c r="W49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X49" s="10" t="n">
         <v>7</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7333,8 +7333,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9645,8 +9645,8 @@
       <c r="P88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -14288,7 +14288,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -14519,7 +14519,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -14618,7 +14618,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14783,7 +14783,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1129,7 +1133,11 @@
       <c r="AB4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1436,7 +1444,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1642,7 +1654,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1844,7 +1860,11 @@
       <c r="AB11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2050,7 +2070,11 @@
       <c r="AB13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2252,7 +2276,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2454,7 +2482,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2654,7 +2686,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2755,7 +2791,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3058,7 +3098,11 @@
       <c r="AB23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3159,7 +3203,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3777,7 +3825,11 @@
       <c r="AB30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4078,7 +4130,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4284,7 +4340,11 @@
       <c r="AB35" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -5310,7 +5370,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5722,7 +5786,11 @@
       <c r="AB49" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6637,7 +6705,11 @@
       <c r="AB58" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6839,7 +6911,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6940,7 +7016,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7443,7 +7523,11 @@
       <c r="AB66" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -8053,7 +8137,11 @@
       <c r="AB72" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8970,7 +9058,11 @@
       <c r="AB81" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9071,7 +9163,11 @@
       <c r="AB82" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9277,7 +9373,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9378,7 +9478,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9891,7 +9995,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10198,7 +10306,11 @@
       <c r="AB93" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10400,7 +10512,11 @@
       <c r="AB95" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 64 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC132"/>
+  <dimension ref="A1:AC133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -996,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="10" t="n">
         <v>3</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1100,8 +1100,8 @@
       <c r="Q4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R4" s="9" t="n">
-        <v>1</v>
+      <c r="R4" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S4" s="10" t="n">
         <v>2</v>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3071,8 +3071,8 @@
       <c r="S23" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T23" s="9" t="n">
-        <v>0</v>
+      <c r="T23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U23" s="9" t="n">
         <v>0</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5545,13 +5545,13 @@
         <v>0</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S47" s="9" t="n">
-        <v>1</v>
+      <c r="S47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T47" s="9" t="n">
         <v>0</v>
@@ -6257,7 +6257,7 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="9" t="n">
         <v>1</v>
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>6619736</v>
+        <v>28680903</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>The Thika Toastmasters</t>
+          <t>Tatu City Toastmasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -8072,10 +8072,10 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8110,8 +8110,8 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="10" t="n">
-        <v>1</v>
+      <c r="T72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U72" s="9" t="n">
         <v>0</v>
@@ -8122,26 +8122,20 @@
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="10" t="n">
-        <v>7</v>
+      <c r="X72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB72" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC72" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB72" s="4" t="n"/>
+      <c r="AC72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8151,19 +8145,19 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28678445</v>
+        <v>6619736</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Chai Toastmasters Club</t>
+          <t>The Thika Toastmasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8177,17 +8171,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8204,10 +8198,10 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8215,14 +8209,14 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8240,9 +8234,13 @@
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8256,15 +8254,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>5954085</v>
+        <v>28678445</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Eldoret Toastmasters</t>
+          <t>Chai Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8278,17 +8276,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8305,10 +8303,10 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8316,26 +8314,26 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="10" t="n">
-        <v>1</v>
+      <c r="T74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="10" t="n">
-        <v>1</v>
+      <c r="Z74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8343,11 +8341,7 @@
       <c r="AB74" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8361,15 +8355,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>5553979</v>
+        <v>5954085</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Kisumu Toastmasters</t>
+          <t>Eldoret Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8383,17 +8377,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8428,27 +8422,31 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y75" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB75" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB75" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8462,15 +8460,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>5913322</v>
+        <v>5553979</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Nakuru Toastmasters Club</t>
+          <t>Kisumu Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8484,10 +8482,10 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>1</v>
@@ -8511,10 +8509,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8522,8 +8520,8 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
@@ -8535,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8547,27 +8545,27 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>7846171</v>
+        <v>5913322</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>5 Speke Road Toastmasters</t>
+          <t>Nakuru Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -8585,25 +8583,25 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O77" s="7" t="inlineStr">
@@ -8612,10 +8610,10 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8630,13 +8628,13 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>0</v>
+      <c r="X77" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8644,11 +8642,11 @@
       <c r="Z77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA77" s="9" t="n">
-        <v>0</v>
+      <c r="AA77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB77" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC77" s="4" t="inlineStr"/>
     </row>
@@ -8664,11 +8662,11 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>28676774</v>
+        <v>7846171</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Cente Toastmasters Club</t>
+          <t>5 Speke Road Toastmasters</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -8686,10 +8684,10 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
         <v>0</v>
@@ -8700,11 +8698,11 @@
         </is>
       </c>
       <c r="M78" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O78" s="7" t="inlineStr">
@@ -8736,8 +8734,8 @@
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="10" t="n">
-        <v>4</v>
+      <c r="X78" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8745,17 +8743,13 @@
       <c r="Z78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA78" s="10" t="n">
-        <v>1</v>
+      <c r="AA78" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8769,11 +8763,11 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>28678857</v>
+        <v>28676774</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Ecobank Uganda Toastmasters Club</t>
+          <t>Cente Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8791,25 +8785,25 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K79" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O79" s="7" t="inlineStr">
@@ -8841,8 +8835,8 @@
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>0</v>
+      <c r="X79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8850,13 +8844,17 @@
       <c r="Z79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA79" s="9" t="n">
-        <v>0</v>
+      <c r="AA79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8870,15 +8868,15 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>28676023</v>
+        <v>28678857</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>High Tea Toastmasters Club</t>
+          <t>Ecobank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8892,17 +8890,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8936,26 +8934,26 @@
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W80" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" s="10" t="n">
-        <v>5</v>
+      <c r="V80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="10" t="n">
-        <v>1</v>
+      <c r="Z80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC80" s="4" t="inlineStr"/>
     </row>
@@ -8971,15 +8969,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>7361841</v>
+        <v>28676023</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Kampala Sunrise Toastmasters</t>
+          <t>High Tea Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8993,13 +8991,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9007,11 +9005,11 @@
         </is>
       </c>
       <c r="M81" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O81" s="7" t="inlineStr">
@@ -9020,31 +9018,31 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T81" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U81" s="10" t="n">
-        <v>1</v>
+      <c r="S81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V81" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W81" s="9" t="n">
-        <v>2</v>
+      <c r="W81" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9052,17 +9050,13 @@
       <c r="Z81" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA81" s="10" t="n">
-        <v>1</v>
+      <c r="AA81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC81" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9076,15 +9070,15 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>3875767</v>
+        <v>7361841</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Kampala Toastmasters Club</t>
+          <t>Kampala Sunrise Toastmasters</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9098,13 +9092,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
@@ -9125,28 +9119,28 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="9" t="n">
-        <v>1</v>
+      <c r="S82" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U82" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="9" t="n">
-        <v>0</v>
+      <c r="U82" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>7</v>
@@ -9154,8 +9148,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9177,19 +9171,19 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28677335</v>
+        <v>3875767</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Absa Bank Uganda Toastmasters Club</t>
+          <t>Kampala Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9203,10 +9197,10 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>0</v>
@@ -9239,10 +9233,10 @@
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U83" s="9" t="n">
         <v>0</v>
@@ -9266,11 +9260,11 @@
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC83" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -9286,15 +9280,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>7659827</v>
+        <v>28677335</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Entebbe Toastmasters Club</t>
+          <t>Absa Bank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9308,13 +9302,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9335,25 +9329,25 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T84" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U84" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9364,18 +9358,18 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="10" t="n">
-        <v>1</v>
+      <c r="Z84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC84" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9391,15 +9385,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>6892375</v>
+        <v>7659827</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Lubowa Toastmasters Club</t>
+          <t>Entebbe Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9413,13 +9407,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9439,26 +9433,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P85" s="10" t="n">
-        <v>5</v>
+      <c r="P85" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q85" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S85" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9469,8 +9463,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9496,15 +9490,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>28678736</v>
+        <v>6892375</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>MU-JHU Toastmasters Club</t>
+          <t>Lubowa Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9518,13 +9512,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9544,29 +9538,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" s="9" t="n">
-        <v>1</v>
+      <c r="P86" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
+      <c r="S86" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="10" t="n">
-        <v>4</v>
+      <c r="V86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9581,9 +9575,13 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9597,15 +9595,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7154422</v>
+        <v>28678736</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Muyenga Toastmasters Club</t>
+          <t>MU-JHU Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9619,17 +9617,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9646,10 +9644,10 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
@@ -9663,14 +9661,14 @@
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="9" t="n">
-        <v>1</v>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9682,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC87" s="4" t="inlineStr"/>
     </row>
@@ -9694,19 +9692,19 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>6633885</v>
+        <v>7154422</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Bukoto Toastmasters</t>
+          <t>Muyenga Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9720,17 +9718,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9749,8 +9747,8 @@
       <c r="P88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" s="10" t="n">
-        <v>2</v>
+      <c r="Q88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9758,14 +9756,14 @@
       <c r="S88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9776,20 +9774,16 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="10" t="n">
-        <v>1</v>
+      <c r="Z88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC88" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9803,15 +9797,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>8001305</v>
+        <v>6633885</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Kampala South Toastmasters Club</t>
+          <t>Bukoto Toastmasters</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9825,10 +9819,10 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>2</v>
@@ -9852,7 +9846,7 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" s="10" t="n">
         <v>2</v>
@@ -9860,14 +9854,14 @@
       <c r="R89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S89" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" s="10" t="n">
-        <v>4</v>
+      <c r="S89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>2</v>
@@ -9876,23 +9870,23 @@
         <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC89" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9908,35 +9902,35 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>6924385</v>
+        <v>8001305</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Ntinda Toastmasters</t>
+          <t>Kampala South Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K90" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F90" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9959,29 +9953,29 @@
       <c r="P90" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" s="9" t="n">
-        <v>1</v>
+      <c r="Q90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S90" s="9" t="n">
-        <v>1</v>
+      <c r="S90" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U90" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X90" s="9" t="n">
-        <v>2</v>
+      <c r="X90" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9993,11 +9987,11 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC90" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10013,15 +10007,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>28680290</v>
+        <v>6924385</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Pillar Toastmasters Club</t>
+          <t>Ntinda Toastmasters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10035,10 +10029,10 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>0</v>
@@ -10062,22 +10056,22 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V91" s="9" t="n">
         <v>0</v>
@@ -10085,8 +10079,8 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="10" t="n">
-        <v>5</v>
+      <c r="X91" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10098,9 +10092,13 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10114,11 +10112,11 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>7955148</v>
+        <v>28680290</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>UNOC Toastmasters Club</t>
+          <t>Pillar Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -10136,10 +10134,10 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>0</v>
@@ -10186,8 +10184,8 @@
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X92" s="9" t="n">
-        <v>3</v>
+      <c r="X92" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10199,13 +10197,9 @@
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10215,19 +10209,19 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>28679448</v>
+        <v>7955148</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Bugolobi Toastmasters Club</t>
+          <t>UNOC Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10241,13 +10235,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10268,10 +10262,10 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10279,20 +10273,20 @@
       <c r="S93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T93" s="10" t="n">
-        <v>1</v>
+      <c r="T93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="10" t="n">
-        <v>4</v>
+      <c r="V93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X93" s="10" t="n">
-        <v>6</v>
+      <c r="X93" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10304,11 +10298,11 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10324,15 +10318,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28680326</v>
+        <v>28679448</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Executives</t>
+          <t>Bugolobi Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10346,13 +10340,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10373,10 +10367,10 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -10384,20 +10378,20 @@
       <c r="S94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="9" t="n">
-        <v>0</v>
+      <c r="V94" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="9" t="n">
-        <v>0</v>
+      <c r="X94" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10409,9 +10403,13 @@
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10425,15 +10423,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28675508</v>
+        <v>28680326</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Exceed Toastmasters</t>
+          <t>Bujumbura Executives</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10447,13 +10445,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
@@ -10473,11 +10471,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P95" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q95" s="10" t="n">
-        <v>2</v>
+      <c r="P95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10485,38 +10483,34 @@
       <c r="S95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T95" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U95" s="10" t="n">
-        <v>1</v>
+      <c r="T95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="10" t="n">
-        <v>5</v>
+      <c r="X95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC95" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10530,15 +10524,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>28675532</v>
+        <v>28675508</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Mbarara Toastmasters Club</t>
+          <t>Exceed Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10552,13 +10546,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10578,32 +10572,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P96" s="9" t="n">
-        <v>1</v>
+      <c r="P96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q96" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R96" s="10" t="n">
-        <v>2</v>
+      <c r="R96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10619,7 +10613,7 @@
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -10635,15 +10629,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28679445</v>
+        <v>28675532</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Red Sea</t>
+          <t>Mbarara Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10657,13 +10651,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10684,13 +10678,13 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q97" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R97" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S97" s="9" t="n">
         <v>0</v>
@@ -10702,25 +10696,31 @@
         <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
+      <c r="X97" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB97" s="4" t="n"/>
-      <c r="AC97" s="4" t="inlineStr"/>
+      <c r="AB97" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10734,11 +10734,11 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28677104</v>
+        <v>28679445</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>UBL Toastmasters Club</t>
+          <t>Red Sea</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -10756,10 +10756,10 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K98" s="4" t="n">
         <v>0</v>
@@ -10806,8 +10806,8 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="10" t="n">
-        <v>5</v>
+      <c r="X98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10818,14 +10818,8 @@
       <c r="AA98" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB98" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC98" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB98" s="4" t="n"/>
+      <c r="AC98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -10835,15 +10829,15 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28679460</v>
+        <v>28677104</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>AIMS RIC</t>
+          <t>UBL Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -10911,8 +10905,8 @@
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+      <c r="X99" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10924,9 +10918,13 @@
         <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10940,15 +10938,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28676457</v>
+        <v>28679460</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Bilingual</t>
+          <t>AIMS RIC</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10962,13 +10960,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10989,7 +10987,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -10998,22 +10996,22 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T100" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>5</v>
+      <c r="X100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -11025,7 +11023,7 @@
         <v>1</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC100" s="4" t="inlineStr"/>
     </row>
@@ -11041,15 +11039,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28676690</v>
+        <v>28676457</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Elevated Speakers Toastmasters Club</t>
+          <t>Bujumbura Bilingual</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11063,17 +11061,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11090,25 +11088,25 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11126,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC101" s="4" t="inlineStr"/>
     </row>
@@ -11142,11 +11140,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>7692944</v>
+        <v>28676690</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Kigali Bilingual Toastmasters Club</t>
+          <t>Elevated Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11164,17 +11162,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11191,7 +11189,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>1</v>
@@ -11209,13 +11207,13 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11227,13 +11225,9 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC102" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11247,11 +11241,11 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>5233390</v>
+        <v>7692944</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Techy Talkers Toastmasters Club</t>
+          <t>Kigali Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -11269,13 +11263,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11296,10 +11290,10 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
@@ -11314,7 +11308,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11332,11 +11326,11 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC103" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -11352,15 +11346,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>5251769</v>
+        <v>5233390</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>TRES Toastmasters Club</t>
+          <t>Techy Talkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11374,13 +11368,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11400,29 +11394,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P104" s="10" t="n">
-        <v>4</v>
+      <c r="P104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T104" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U104" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V104" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>7</v>
@@ -11430,42 +11424,42 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC104" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28677895</v>
+        <v>5251769</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Imperium Toastmasters Club</t>
+          <t>TRES Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11479,13 +11473,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11505,29 +11499,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P105" s="9" t="n">
-        <v>0</v>
+      <c r="P105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U105" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11535,14 +11529,20 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB105" s="4" t="n"/>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AB105" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11556,15 +11556,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7863227</v>
+        <v>28677895</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Mauritius Revenue Authority</t>
+          <t>Imperium Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11581,10 +11581,10 @@
         <v>29</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11623,19 +11623,19 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X106" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="10" t="n">
-        <v>1</v>
+      <c r="Z106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11655,11 +11655,11 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28675654</v>
+        <v>7863227</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>NBA Toastmasters Club</t>
+          <t>Mauritius Revenue Authority</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
@@ -11677,13 +11677,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11722,13 +11722,13 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11754,11 +11754,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>2558</v>
+        <v>28675654</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Port Louis Toastmasters Club</t>
+          <t>NBA Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11776,13 +11776,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11806,13 +11806,13 @@
         <v>1</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" s="9" t="n">
         <v>0</v>
@@ -11821,13 +11821,13 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11849,19 +11849,19 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28675649</v>
+        <v>2558</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Bagatelle Toastmasters Club</t>
+          <t>Port Louis Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11878,10 +11878,10 @@
         <v>43</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11902,16 +11902,16 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11919,14 +11919,14 @@
       <c r="U109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W109" s="10" t="n">
+      <c r="V109" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="10" t="n">
         <v>5</v>
-      </c>
-      <c r="X109" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11952,11 +11952,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1226180</v>
+        <v>28675649</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Financial Toastmasters Club</t>
+          <t>Bagatelle Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11974,13 +11974,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -12010,19 +12010,19 @@
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U110" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V110" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W110" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -12051,15 +12051,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28680744</v>
+        <v>1226180</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>IQ-EQ Mauritius Toastmasters Club</t>
+          <t>Financial Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12073,13 +12073,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12109,22 +12109,22 @@
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>0</v>
+      <c r="X111" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12150,15 +12150,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>592015</v>
+        <v>28680744</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Plateau Toastmasters Club</t>
+          <t>IQ-EQ Mauritius Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12172,13 +12172,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12210,20 +12210,20 @@
       <c r="S112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="10" t="n">
-        <v>4</v>
+      <c r="V112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X112" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12249,11 +12249,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28679140</v>
+        <v>592015</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Standard Bank (Mauritius) Limited</t>
+          <t>Plateau Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12271,13 +12271,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12309,8 +12309,8 @@
       <c r="S113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T113" s="9" t="n">
-        <v>0</v>
+      <c r="T113" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U113" s="9" t="n">
         <v>0</v>
@@ -12318,11 +12318,11 @@
       <c r="V113" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W113" s="10" t="n">
-        <v>6</v>
+      <c r="W113" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12344,19 +12344,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>5438132</v>
+        <v>28679140</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>NewGen Toastmasters Club</t>
+          <t>Standard Bank (Mauritius) Limited</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12370,17 +12370,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L114" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>10</v>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12414,14 +12414,14 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W114" s="9" t="n">
-        <v>0</v>
+      <c r="V114" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W114" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12447,11 +12447,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>7235882</v>
+        <v>5438132</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>PoWerCommunicators Toastmasters Club</t>
+          <t>NewGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12469,17 +12469,17 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L115" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M115" s="8" t="n">
@@ -12496,10 +12496,10 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" s="9" t="n">
         <v>0</v>
@@ -12514,13 +12514,13 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12546,15 +12546,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28679751</v>
+        <v>7235882</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Royal Toastmasters Club</t>
+          <t>PoWerCommunicators Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12595,10 +12595,10 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -12613,19 +12613,19 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>1</v>
+      <c r="X116" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12645,15 +12645,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>28675608</v>
+        <v>28679751</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>RSS Toastmasters Academy</t>
+          <t>Royal Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12667,17 +12667,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12712,19 +12712,19 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X117" s="10" t="n">
-        <v>7</v>
+      <c r="X117" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -12740,43 +12740,43 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>7335249</v>
+        <v>28675608</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>ACE Speakers Toastmasters</t>
+          <t>RSS Toastmasters Academy</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J118" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K118" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F118" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="J118" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12793,25 +12793,25 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="Q118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U118" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V118" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
@@ -12843,15 +12843,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>2645756</v>
+        <v>7335249</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Aurora Toastmasters Club</t>
+          <t>ACE Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12865,13 +12865,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12906,17 +12906,17 @@
       <c r="T119" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U119" s="9" t="n">
-        <v>0</v>
+      <c r="U119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12942,15 +12942,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>7864607</v>
+        <v>2645756</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>ELIO Toastmasters Club</t>
+          <t>Aurora Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12964,10 +12964,10 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>3</v>
@@ -12990,23 +12990,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P120" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q120" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R120" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S120" s="10" t="n">
-        <v>3</v>
+      <c r="P120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T120" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U120" s="10" t="n">
-        <v>2</v>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
         <v>3</v>
@@ -13015,7 +13015,7 @@
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13041,15 +13041,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28679278</v>
+        <v>7864607</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Pearls of Expression Toastmasters Club</t>
+          <t>ELIO Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13063,13 +13063,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13089,32 +13089,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P121" s="9" t="n">
+      <c r="P121" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S121" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="10" t="n">
-        <v>4</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U121" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V121" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X121" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13140,15 +13140,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28679212</v>
+        <v>28679278</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Telfair Toastmasters Club</t>
+          <t>Pearls of Expression Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13162,17 +13162,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>0</v>
@@ -13206,20 +13206,20 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>0</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X122" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13235,15 +13235,15 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28677974</v>
+        <v>28679212</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Axian Red Toastmasters Club</t>
+          <t>Telfair Toastmasters Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -13261,10 +13261,10 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K123" s="4" t="n">
         <v>0</v>
@@ -13275,11 +13275,11 @@
         </is>
       </c>
       <c r="M123" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N123" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O123" s="7" t="inlineStr">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -13311,17 +13311,17 @@
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="9" t="n">
-        <v>2</v>
+      <c r="X123" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB123" s="4" t="n"/>
       <c r="AC123" s="4" t="inlineStr"/>
@@ -13338,15 +13338,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28677814</v>
+        <v>28677974</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Go BNI Toastmasters Club</t>
+          <t>Axian Red Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K124" s="4" t="n">
         <v>0</v>
@@ -13374,11 +13374,11 @@
         </is>
       </c>
       <c r="M124" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N124" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O124" s="7" t="inlineStr">
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="X124" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13419,8 +13419,8 @@
       <c r="Z124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA124" s="10" t="n">
-        <v>1</v>
+      <c r="AA124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB124" s="4" t="n"/>
       <c r="AC124" s="4" t="inlineStr"/>
@@ -13437,15 +13437,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28676664</v>
+        <v>28677814</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Outstanding Toastmasters Club</t>
+          <t>Go BNI Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13459,17 +13459,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13489,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="Q125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R125" s="9" t="n">
         <v>0</v>
@@ -13497,20 +13497,20 @@
       <c r="S125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T125" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U125" s="10" t="n">
-        <v>1</v>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" s="10" t="n">
-        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13536,11 +13536,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7010199</v>
+        <v>28676664</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>The First Toastmasters Club of  Madagascar</t>
+          <t>Outstanding Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -13558,13 +13558,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13588,28 +13588,28 @@
         <v>0</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" s="10" t="n">
-        <v>4</v>
+      <c r="U126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V126" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13631,19 +13631,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28676459</v>
+        <v>7010199</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Airtel Madagascar Toastmasters Club</t>
+          <t>The First Toastmasters Club of  Madagascar</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13657,25 +13657,25 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N127" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O127" s="7" t="inlineStr">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13693,31 +13693,31 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>0</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>0</v>
+      <c r="X127" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB127" s="4" t="n"/>
       <c r="AC127" s="4" t="inlineStr"/>
@@ -13734,11 +13734,11 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28677906</v>
+        <v>28676459</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Madacan Toastmasters Club</t>
+          <t>Airtel Madagascar Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13833,11 +13833,11 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28676681</v>
+        <v>28677906</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Mirongo Toastmasters of Toamasina</t>
+          <t>Madacan Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13855,13 +13855,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13869,11 +13869,11 @@
         </is>
       </c>
       <c r="M129" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -13900,13 +13900,13 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="10" t="n">
-        <v>5</v>
+      <c r="X129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13914,8 +13914,8 @@
       <c r="Z129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA129" s="10" t="n">
-        <v>1</v>
+      <c r="AA129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB129" s="4" t="n"/>
       <c r="AC129" s="4" t="inlineStr"/>
@@ -13932,15 +13932,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28679267</v>
+        <v>28676681</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Solitaire Toastmasters Club</t>
+          <t>Mirongo Toastmasters of Toamasina</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13954,17 +13954,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13998,20 +13998,20 @@
       <c r="U130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="10" t="n">
-        <v>4</v>
+      <c r="V130" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="10" t="n">
-        <v>1</v>
+      <c r="Z130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA130" s="10" t="n">
         <v>1</v>
@@ -14031,15 +14031,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28675645</v>
+        <v>28679267</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Tsingy Toastmasters Club</t>
+          <t>Solitaire Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14053,13 +14053,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14080,31 +14080,31 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W131" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W131" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X131" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -14130,15 +14130,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28675795</v>
+        <v>28675645</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Young Challengers Toastmasters Club</t>
+          <t>Tsingy Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14152,10 +14152,10 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>1</v>
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>1</v>
@@ -14194,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="U132" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V132" s="9" t="n">
         <v>1</v>
@@ -14208,8 +14208,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14217,8 +14217,107 @@
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="4" t="inlineStr"/>
     </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="n">
+        <v>28675795</v>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>Young Challengers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K133" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M133" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V133" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="4" t="n"/>
+      <c r="AC133" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC132"/>
+  <autoFilter ref="A1:AC133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14305,7 +14404,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -14437,7 +14536,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -14602,7 +14701,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14764,16 +14863,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -14782,7 +14881,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -14899,7 +14998,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14965,13 +15064,13 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -15163,7 +15262,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 29 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC134"/>
+  <dimension ref="A1:AC137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
@@ -1004,11 +1004,11 @@
       <c r="T3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="9" t="n">
-        <v>0</v>
+      <c r="U3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1220,8 +1220,8 @@
       <c r="V5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>0</v>
+      <c r="W5" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1478,13 +1478,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1583,17 +1583,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1735,8 +1735,8 @@
       <c r="V10" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>3</v>
+      <c r="W10" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -1894,13 +1894,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="10" t="n">
         <v>1</v>
@@ -1999,13 +1999,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2148,8 +2148,8 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>1</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2209,17 +2209,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="8" t="n">
@@ -2310,17 +2310,17 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M16" s="8" t="n">
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>7</v>
@@ -2720,17 +2720,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2825,13 +2825,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>4</v>
       </c>
       <c r="W21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X21" s="10" t="n">
         <v>7</v>
@@ -2930,17 +2930,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="8" t="n">
@@ -3132,17 +3132,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="8" t="n">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3281,11 +3281,11 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>0</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W25" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3443,17 +3443,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3487,8 +3487,8 @@
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="9" t="n">
-        <v>3</v>
+      <c r="V27" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3604,8 +3604,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3653,17 +3653,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3859,17 +3859,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4164,17 +4164,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4205,11 +4205,11 @@
       <c r="T34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="9" t="n">
-        <v>2</v>
+      <c r="U34" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-11</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>75</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
+        <v>-20</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4406,8 +4406,8 @@
       <c r="Q36" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R36" s="9" t="n">
-        <v>1</v>
+      <c r="R36" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S36" s="10" t="n">
         <v>2</v>
@@ -4418,11 +4418,11 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W36" s="9" t="n">
-        <v>0</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>7</v>
@@ -4465,7 +4465,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4479,13 +4479,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4523,11 +4523,11 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>6</v>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>2</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4681,17 +4681,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-31</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4887,13 +4887,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4978,7 +4978,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4992,17 +4992,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5027,14 +5027,14 @@
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="9" t="n">
-        <v>1</v>
+      <c r="S42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T42" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V42" s="9" t="n">
         <v>0</v>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5404,17 +5404,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5509,13 +5509,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5658,8 +5658,8 @@
       <c r="U48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="9" t="n">
-        <v>3</v>
+      <c r="V48" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5715,17 +5715,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5820,13 +5820,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>8</v>
+        <v>-22</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5855,8 +5855,8 @@
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>0</v>
+      <c r="S50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
@@ -5868,7 +5868,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -5903,15 +5903,15 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>28677731</v>
+        <v>28680953</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Juhudi Toastmasters Club</t>
+          <t>Hug a Mug Toastmasters Club</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5925,25 +5925,25 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O51" s="7" t="inlineStr">
@@ -5976,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="X51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5984,12 +5984,10 @@
       <c r="Z51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AA51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="4" t="n"/>
       <c r="AC51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
@@ -6004,11 +6002,11 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>28677725</v>
+        <v>28677731</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Kinara</t>
+          <t>Juhudi Toastmasters Club</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -6026,17 +6024,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6089,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="4" t="inlineStr"/>
     </row>
@@ -6105,15 +6103,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>7655679</v>
+        <v>28677725</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Masaki's Executive Toastmasters Club</t>
+          <t>Kinara</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6127,70 +6125,70 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K53" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M53" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O53" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="9" t="n">
+      <c r="Y53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="W53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA53" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB53" s="4" t="n">
-        <v>5</v>
       </c>
       <c r="AC53" s="4" t="inlineStr"/>
     </row>
@@ -6206,15 +6204,15 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>7229265</v>
+        <v>7655679</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Mount Meru</t>
+          <t>Masaki's Executive Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6228,17 +6226,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6255,32 +6253,32 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="10" t="n">
+      <c r="V54" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W54" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X54" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
@@ -6291,31 +6289,31 @@
         <v>1</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AC54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>28679585</v>
+        <v>7229265</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Kasarani Toastmasters Club</t>
+          <t>Mount Meru</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6329,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6356,16 +6354,16 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q55" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q55" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" s="10" t="n">
         <v>1</v>
@@ -6373,14 +6371,14 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W55" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X55" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6392,13 +6390,9 @@
         <v>1</v>
       </c>
       <c r="AB55" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC55" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6412,15 +6406,15 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>28679879</v>
+        <v>28679585</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>LifeSMART Toastmasters Club</t>
+          <t>Kasarani Toastmasters Club</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6434,17 +6428,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6461,10 +6455,10 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6472,32 +6466,38 @@
       <c r="S56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>0</v>
+      <c r="X56" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB56" s="4" t="n"/>
-      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AB56" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6511,15 +6511,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>28679350</v>
+        <v>28679879</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Momentum Toastmasters Club</t>
+          <t>LifeSMART Toastmasters Club</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>0</v>
@@ -6589,15 +6589,13 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB57" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB57" s="4" t="n"/>
       <c r="AC57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
@@ -6612,15 +6610,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>28678419</v>
+        <v>28679350</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Runda Elite Toastmasters Club</t>
+          <t>Momentum Toastmasters Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6634,17 +6632,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6660,17 +6658,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P58" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q58" s="10" t="n">
-        <v>2</v>
+      <c r="P58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -6678,32 +6676,28 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="10" t="n">
-        <v>4</v>
+      <c r="V58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X58" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="10" t="n">
-        <v>1</v>
+      <c r="Z58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6717,15 +6711,15 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1202269</v>
+        <v>28678419</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>Runda Elite Toastmasters Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6739,13 +6733,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6765,17 +6759,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="9" t="n">
-        <v>1</v>
+      <c r="P59" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q59" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6786,8 +6780,8 @@
       <c r="V59" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W59" s="9" t="n">
-        <v>0</v>
+      <c r="W59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X59" s="10" t="n">
         <v>7</v>
@@ -6802,11 +6796,11 @@
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC59" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -6818,19 +6812,19 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>28675568</v>
+        <v>1202269</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Bamburi Toastmasters Club</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6844,25 +6838,25 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O60" s="7" t="inlineStr">
@@ -6874,13 +6868,13 @@
         <v>0</v>
       </c>
       <c r="Q60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -6888,28 +6882,32 @@
       <c r="U60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="9" t="n">
-        <v>0</v>
+      <c r="V60" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W60" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X60" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6923,11 +6921,11 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>7946880</v>
+        <v>28675568</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Blue Eagles Toastmasters Club</t>
+          <t>Bamburi Toastmasters Club</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6945,25 +6943,25 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -6972,49 +6970,45 @@
         </is>
       </c>
       <c r="P61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7028,15 +7022,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1197334</v>
+        <v>7946880</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Nairobi Toastmasters</t>
+          <t>Blue Eagles Toastmasters Club</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7050,10 +7044,10 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>0</v>
@@ -7077,7 +7071,7 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q62" s="9" t="n">
         <v>0</v>
@@ -7088,20 +7082,20 @@
       <c r="S62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T62" s="10" t="n">
-        <v>1</v>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W62" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X62" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -7133,15 +7127,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>28680199</v>
+        <v>1197334</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Power Talk Toastmasters</t>
+          <t>Nairobi Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7149,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7182,7 +7176,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7191,19 +7185,19 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>0</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -7211,16 +7205,20 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7234,15 +7232,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>6639074</v>
+        <v>28680199</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Rafiki Toastmasters</t>
+          <t>Power Talk Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7256,13 +7254,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7283,10 +7281,10 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q64" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7300,26 +7298,26 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="10" t="n">
-        <v>4</v>
+      <c r="V64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X64" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="10" t="n">
-        <v>1</v>
+      <c r="Z64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC64" s="4" t="inlineStr"/>
     </row>
@@ -7335,15 +7333,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>28680756</v>
+        <v>6639074</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Safaricom Toastmasters Club</t>
+          <t>Rafiki Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7357,17 +7355,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7384,10 +7382,10 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q65" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7401,14 +7399,14 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>0</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7419,7 +7417,9 @@
       <c r="AA65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB65" s="4" t="n"/>
+      <c r="AB65" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="AC65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
@@ -7430,15 +7430,15 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>28679092</v>
+        <v>28680756</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>MRM BS Toastmasters Club</t>
+          <t>Safaricom Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7518,9 +7518,7 @@
       <c r="AA66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB66" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB66" s="4" t="n"/>
       <c r="AC66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
@@ -7535,15 +7533,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>5789341</v>
+        <v>28679092</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Nairobi Bottlers</t>
+          <t>MRM BS Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7557,17 +7555,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7584,10 +7582,10 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
@@ -7602,13 +7600,13 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7620,13 +7618,9 @@
         <v>1</v>
       </c>
       <c r="AB67" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC67" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7640,15 +7634,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>28676279</v>
+        <v>5789341</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Strathmore University Toastmasters</t>
+          <t>Nairobi Bottlers</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7662,17 +7656,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7689,10 +7683,10 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q68" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
@@ -7706,28 +7700,32 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="9" t="n">
-        <v>0</v>
+      <c r="V68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC68" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7741,15 +7739,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>5011794</v>
+        <v>28676279</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>TOASTMASTERS@CHIROMO</t>
+          <t>Strathmore University Toastmasters</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7763,17 +7761,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7790,49 +7788,45 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB69" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Q69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC69" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7842,19 +7836,19 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>28677212</v>
+        <v>5011794</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Juja Toastmasters Club</t>
+          <t>TOASTMASTERS@CHIROMO</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7868,17 +7862,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7895,7 +7889,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>1</v>
@@ -7909,17 +7903,17 @@
       <c r="T70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V70" s="10" t="n">
-        <v>4</v>
+      <c r="U70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7931,9 +7925,13 @@
         <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7947,15 +7945,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>6613258</v>
+        <v>28677212</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Kilele Toastmasters Club</t>
+          <t>Juja Toastmasters Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7969,10 +7967,10 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K71" s="4" t="n">
         <v>3</v>
@@ -8005,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" s="10" t="n">
         <v>1</v>
@@ -8013,11 +8011,11 @@
       <c r="U71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V71" s="9" t="n">
-        <v>3</v>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>7</v>
@@ -8032,7 +8030,7 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC71" s="4" t="inlineStr"/>
     </row>
@@ -8048,15 +8046,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>7474799</v>
+        <v>6613258</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Meru Toastmasters</t>
+          <t>Kilele Toastmasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8073,10 +8071,10 @@
         <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8097,10 +8095,10 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -8108,32 +8106,32 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="9" t="n">
-        <v>3</v>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="9" t="n">
-        <v>0</v>
+      <c r="Z72" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC72" s="4" t="inlineStr"/>
     </row>
@@ -8149,15 +8147,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28680903</v>
+        <v>7474799</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Tatu City Toastmasters Club</t>
+          <t>Meru Toastmasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8171,17 +8169,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8216,24 +8214,26 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X73" s="9" t="n">
-        <v>0</v>
+      <c r="X73" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="10" t="n">
-        <v>1</v>
+      <c r="Z73" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB73" s="4" t="n"/>
+      <c r="AB73" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AC73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
@@ -8248,15 +8248,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>6619736</v>
+        <v>28680903</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>The Thika Toastmasters</t>
+          <t>Tatu City Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8270,13 +8270,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>0</v>
@@ -8308,20 +8308,20 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="10" t="n">
-        <v>1</v>
+      <c r="T74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="10" t="n">
-        <v>7</v>
+      <c r="X74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8332,14 +8332,8 @@
       <c r="AA74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB74" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC74" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB74" s="4" t="n"/>
+      <c r="AC74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8349,19 +8343,19 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28678445</v>
+        <v>6619736</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Chai Toastmasters Club</t>
+          <t>The Thika Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8375,13 +8369,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8402,10 +8396,10 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8413,8 +8407,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8438,9 +8432,13 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8454,11 +8452,11 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>5954085</v>
+        <v>28678445</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Eldoret Toastmasters</t>
+          <t>Chai Toastmasters Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -8476,17 +8474,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8503,10 +8501,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q76" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8514,20 +8512,20 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="10" t="n">
-        <v>1</v>
+      <c r="T76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8541,11 +8539,7 @@
       <c r="AB76" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8559,11 +8553,11 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>5553979</v>
+        <v>5954085</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Kisumu Toastmasters</t>
+          <t>Eldoret Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -8581,13 +8575,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8626,27 +8620,31 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8660,11 +8658,11 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>5913322</v>
+        <v>5553979</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Nakuru Toastmasters Club</t>
+          <t>Kisumu Toastmasters</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -8682,13 +8680,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8709,31 +8707,31 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8745,31 +8743,31 @@
         <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>7846171</v>
+        <v>5913322</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>5 Speke Road Toastmasters</t>
+          <t>Nakuru Toastmasters Club</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8783,25 +8781,25 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O79" s="7" t="inlineStr">
@@ -8810,10 +8808,10 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8821,32 +8819,32 @@
       <c r="S79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="9" t="n">
-        <v>0</v>
+      <c r="V79" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X79" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC79" s="4" t="inlineStr"/>
     </row>
@@ -8862,11 +8860,11 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>28676774</v>
+        <v>7846171</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Cente Toastmasters Club</t>
+          <t>5 Speke Road Toastmasters</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -8884,25 +8882,25 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O80" s="7" t="inlineStr">
@@ -8934,8 +8932,8 @@
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="10" t="n">
-        <v>4</v>
+      <c r="X80" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8943,17 +8941,13 @@
       <c r="Z80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA80" s="10" t="n">
-        <v>1</v>
+      <c r="AA80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC80" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -8967,11 +8961,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28678857</v>
+        <v>28676774</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Ecobank Uganda Toastmasters Club</t>
+          <t>Cente Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -8989,13 +8983,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9003,11 +8997,11 @@
         </is>
       </c>
       <c r="M81" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O81" s="7" t="inlineStr">
@@ -9039,8 +9033,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="9" t="n">
-        <v>0</v>
+      <c r="X81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9048,13 +9042,17 @@
       <c r="Z81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA81" s="9" t="n">
-        <v>0</v>
+      <c r="AA81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC81" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC81" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9068,15 +9066,15 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>28676023</v>
+        <v>28678857</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>High Tea Toastmasters Club</t>
+          <t>Ecobank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9090,17 +9088,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9134,26 +9132,26 @@
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W82" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X82" s="10" t="n">
-        <v>5</v>
+      <c r="V82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="10" t="n">
-        <v>1</v>
+      <c r="Z82" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC82" s="4" t="inlineStr"/>
     </row>
@@ -9169,15 +9167,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>7361841</v>
+        <v>28676023</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Kampala Sunrise Toastmasters</t>
+          <t>High Tea Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9191,13 +9189,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9205,11 +9203,11 @@
         </is>
       </c>
       <c r="M83" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O83" s="7" t="inlineStr">
@@ -9218,31 +9216,31 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S83" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T83" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U83" s="10" t="n">
-        <v>1</v>
+      <c r="S83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V83" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W83" s="9" t="n">
-        <v>2</v>
+      <c r="W83" s="10" t="n">
+        <v>11</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9250,17 +9248,13 @@
       <c r="Z83" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA83" s="10" t="n">
-        <v>1</v>
+      <c r="AA83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC83" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9274,15 +9268,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>3875767</v>
+        <v>7361841</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Kampala Toastmasters Club</t>
+          <t>Kampala Sunrise Toastmasters</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9296,13 +9290,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9323,28 +9317,28 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="9" t="n">
-        <v>1</v>
+      <c r="S84" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V84" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W84" s="9" t="n">
-        <v>0</v>
+      <c r="U84" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W84" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>7</v>
@@ -9375,19 +9369,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>28677335</v>
+        <v>3875767</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Absa Bank Uganda Toastmasters Club</t>
+          <t>Kampala Toastmasters Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9401,17 +9395,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9437,19 +9431,19 @@
         <v>0</v>
       </c>
       <c r="S85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>7</v>
@@ -9464,11 +9458,11 @@
         <v>1</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC85" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -9484,15 +9478,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7659827</v>
+        <v>28677335</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Entebbe Toastmasters Club</t>
+          <t>Absa Bank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9506,13 +9500,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9533,28 +9527,28 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R86" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S86" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U86" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V86" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="S86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W86" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9569,11 +9563,11 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9589,15 +9583,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>6892375</v>
+        <v>7659827</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Lubowa Toastmasters Club</t>
+          <t>Entebbe Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9611,13 +9605,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9637,29 +9631,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P87" s="10" t="n">
-        <v>5</v>
+      <c r="P87" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q87" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="9" t="n">
-        <v>0</v>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>7</v>
@@ -9694,15 +9688,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>28678736</v>
+        <v>6892375</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>MU-JHU Toastmasters Club</t>
+          <t>Lubowa Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9716,17 +9710,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9742,29 +9736,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q88" s="9" t="n">
-        <v>1</v>
+      <c r="P88" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" s="10" t="n">
-        <v>1</v>
+      <c r="S88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="10" t="n">
-        <v>4</v>
+      <c r="V88" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9779,9 +9773,13 @@
         <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9795,15 +9793,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>7154422</v>
+        <v>28678736</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Muyenga Toastmasters Club</t>
+          <t>MU-JHU Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9817,13 +9815,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9844,10 +9842,10 @@
         </is>
       </c>
       <c r="P89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
@@ -9861,14 +9859,14 @@
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>1</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9880,7 +9878,7 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC89" s="4" t="inlineStr"/>
     </row>
@@ -9892,15 +9890,15 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>6633885</v>
+        <v>7154422</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Bukoto Toastmasters</t>
+          <t>Muyenga Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -9918,17 +9916,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L90" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="8" t="n">
@@ -9947,8 +9945,8 @@
       <c r="P90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" s="10" t="n">
-        <v>2</v>
+      <c r="Q90" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9956,20 +9954,20 @@
       <c r="S90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9981,13 +9979,9 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC90" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10001,15 +9995,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>8001305</v>
+        <v>6633885</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Kampala South Toastmasters Club</t>
+          <t>Bukoto Toastmasters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10023,17 +10017,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10050,7 +10044,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="10" t="n">
         <v>2</v>
@@ -10058,23 +10052,23 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T91" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" s="10" t="n">
+      <c r="S91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V91" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10086,11 +10080,11 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC91" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -10106,15 +10100,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>6924385</v>
+        <v>8001305</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Ntinda Toastmasters</t>
+          <t>Kampala South Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10128,17 +10122,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10163,23 +10157,23 @@
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="9" t="n">
-        <v>1</v>
+      <c r="S92" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T92" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U92" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10191,11 +10185,11 @@
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10211,15 +10205,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>28680290</v>
+        <v>6924385</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Pillar Toastmasters Club</t>
+          <t>Ntinda Toastmasters</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10233,17 +10227,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10260,31 +10254,31 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q93" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10296,9 +10290,13 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC93" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC93" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10312,15 +10310,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7955148</v>
+        <v>28680290</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>UNOC Toastmasters Club</t>
+          <t>Pillar Toastmasters Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10334,10 +10332,10 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K94" s="4" t="n">
         <v>0</v>
@@ -10390,20 +10388,16 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10413,19 +10407,19 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>28679448</v>
+        <v>7955148</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Bugolobi Toastmasters Club</t>
+          <t>UNOC Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10439,17 +10433,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-33</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10466,10 +10460,10 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
@@ -10477,36 +10471,36 @@
       <c r="S95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T95" s="10" t="n">
-        <v>1</v>
+      <c r="T95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
-        <v>4</v>
+      <c r="V95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X95" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="10" t="n">
-        <v>1</v>
+      <c r="Z95" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC95" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10522,15 +10516,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>28680326</v>
+        <v>28679448</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Executives</t>
+          <t>Bugolobi Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10544,17 +10538,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10571,10 +10565,10 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10582,34 +10576,38 @@
       <c r="S96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="9" t="n">
-        <v>0</v>
+      <c r="T96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X96" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10623,15 +10621,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28675508</v>
+        <v>28680326</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Exceed Toastmasters</t>
+          <t>Bujumbura Executives</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10645,13 +10643,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10671,50 +10669,46 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P97" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q97" s="10" t="n">
-        <v>2</v>
+      <c r="P97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="10" t="n">
-        <v>6</v>
+      <c r="X97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="10" t="n">
-        <v>1</v>
+      <c r="Z97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC97" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10728,15 +10722,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28675532</v>
+        <v>28675508</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Mbarara Toastmasters Club</t>
+          <t>Exceed Toastmasters</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10750,17 +10744,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10776,26 +10770,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P98" s="9" t="n">
-        <v>1</v>
+      <c r="P98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q98" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R98" s="10" t="n">
+      <c r="R98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V98" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10817,7 +10811,7 @@
       </c>
       <c r="AC98" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -10833,15 +10827,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28679445</v>
+        <v>28675532</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Red Sea</t>
+          <t>Mbarara Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10855,17 +10849,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10882,13 +10876,13 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q99" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R99" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S99" s="9" t="n">
         <v>0</v>
@@ -10900,25 +10894,31 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X99" s="9" t="n">
-        <v>0</v>
+      <c r="X99" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB99" s="4" t="n"/>
-      <c r="AC99" s="4" t="inlineStr"/>
+      <c r="AB99" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10932,11 +10932,11 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28677104</v>
+        <v>28679445</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>UBL Toastmasters Club</t>
+          <t>Red Sea</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -10954,10 +10954,10 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K100" s="4" t="n">
         <v>0</v>
@@ -11004,8 +11004,8 @@
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>5</v>
+      <c r="X100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
@@ -11016,14 +11016,8 @@
       <c r="AA100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB100" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC100" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB100" s="4" t="n"/>
+      <c r="AC100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11033,15 +11027,15 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28679460</v>
+        <v>28677104</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>AIMS RIC</t>
+          <t>UBL Toastmasters Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -11059,17 +11053,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11109,8 +11103,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>0</v>
+      <c r="X101" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11122,9 +11116,13 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11138,15 +11136,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28676457</v>
+        <v>28679460</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Bilingual</t>
+          <t>AIMS RIC</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11160,17 +11158,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11187,7 +11185,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -11196,22 +11194,22 @@
         <v>0</v>
       </c>
       <c r="S102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T102" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="10" t="n">
-        <v>5</v>
+      <c r="X102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11223,7 +11221,7 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC102" s="4" t="inlineStr"/>
     </row>
@@ -11239,15 +11237,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28676690</v>
+        <v>28676457</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Elevated Speakers Toastmasters Club</t>
+          <t>Bujumbura Bilingual</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11261,13 +11259,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>1</v>
+        <v>-9</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11288,31 +11286,31 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X103" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11324,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC103" s="4" t="inlineStr"/>
     </row>
@@ -11340,15 +11338,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>7692944</v>
+        <v>28676690</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Kigali Bilingual Toastmasters Club</t>
+          <t>Elevated Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11362,17 +11360,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11389,49 +11387,45 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC104" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11445,15 +11439,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>5233390</v>
+        <v>7692944</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Techy Talkers Toastmasters Club</t>
+          <t>Kigali Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11467,17 +11461,17 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L105" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M105" s="8" t="n">
@@ -11494,16 +11488,16 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -11511,11 +11505,11 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>0</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>7</v>
@@ -11530,11 +11524,11 @@
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC105" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -11550,15 +11544,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>5251769</v>
+        <v>5233390</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>TRES Toastmasters Club</t>
+          <t>Techy Talkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11572,13 +11566,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11598,29 +11592,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P106" s="10" t="n">
-        <v>5</v>
+      <c r="P106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V106" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11635,35 +11629,35 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28677895</v>
+        <v>5251769</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Imperium Toastmasters Club</t>
+          <t>TRES Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11677,17 +11671,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11703,29 +11697,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P107" s="9" t="n">
-        <v>0</v>
+      <c r="P107" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W107" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11739,8 +11733,14 @@
       <c r="AA107" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB107" s="4" t="n"/>
-      <c r="AC107" s="4" t="inlineStr"/>
+      <c r="AB107" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11754,11 +11754,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>7863227</v>
+        <v>28677895</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Mauritius Revenue Authority</t>
+          <t>Imperium Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -11776,13 +11776,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J108" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="J108" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11821,13 +11821,13 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X108" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11853,11 +11853,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28675654</v>
+        <v>7863227</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>NBA Toastmasters Club</t>
+          <t>Mauritius Revenue Authority</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11878,10 +11878,10 @@
         <v>20</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
         <v>0</v>
@@ -11920,13 +11920,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11952,11 +11952,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>2558</v>
+        <v>28675654</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Port Louis Toastmasters Club</t>
+          <t>NBA Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11974,17 +11974,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L110" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12004,13 +12004,13 @@
         <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" s="9" t="n">
         <v>0</v>
@@ -12019,13 +12019,13 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12047,19 +12047,19 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28675649</v>
+        <v>28681044</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Bagatelle Toastmasters Club</t>
+          <t>Ocorian NewGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12073,13 +12073,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12117,14 +12117,14 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W111" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X111" s="10" t="n">
-        <v>7</v>
+      <c r="V111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12146,19 +12146,19 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1226180</v>
+        <v>28681048</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Financial Toastmasters Club</t>
+          <t>Ocorian NexGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12172,13 +12172,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         </is>
       </c>
       <c r="P112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q112" s="9" t="n">
         <v>0</v>
@@ -12208,22 +12208,22 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T112" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U112" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="10" t="n">
-        <v>7</v>
+      <c r="X112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
@@ -12245,15 +12245,15 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28680744</v>
+        <v>2558</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>IQ-EQ Mauritius Toastmasters Club</t>
+          <t>Port Louis Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12271,13 +12271,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12298,16 +12298,16 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12316,13 +12316,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>0</v>
+      <c r="X113" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12348,15 +12348,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>592015</v>
+        <v>28675649</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Plateau Toastmasters Club</t>
+          <t>Bagatelle Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12370,13 +12370,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12408,20 +12408,20 @@
       <c r="S114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T114" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="n">
-        <v>1</v>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V114" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W114" s="9" t="n">
-        <v>1</v>
+      <c r="W114" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12447,11 +12447,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28679140</v>
+        <v>1226180</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Standard Bank (Mauritius) Limited</t>
+          <t>Financial Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12469,13 +12469,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12505,22 +12505,22 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W115" s="10" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="T115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V115" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12542,15 +12542,15 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>5438132</v>
+        <v>28680744</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>NewGen Toastmasters Club</t>
+          <t>IQ-EQ Mauritius Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -12568,17 +12568,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L116" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12613,13 +12613,13 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="10" t="n">
-        <v>7</v>
+      <c r="X116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12641,19 +12641,19 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>7235882</v>
+        <v>592015</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>PoWerCommunicators Toastmasters Club</t>
+          <t>Plateau Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12667,17 +12667,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K117" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12694,10 +12694,10 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12705,20 +12705,20 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="9" t="n">
-        <v>1</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12740,19 +12740,19 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>28679751</v>
+        <v>28679140</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Royal Toastmasters Club</t>
+          <t>Standard Bank (Mauritius) Limited</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12766,13 +12766,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12810,14 +12810,14 @@
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X118" s="9" t="n">
-        <v>1</v>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W118" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X118" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12843,11 +12843,11 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28675608</v>
+        <v>5438132</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>RSS Toastmasters Academy</t>
+          <t>NewGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -12865,13 +12865,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
@@ -12938,19 +12938,19 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>7335249</v>
+        <v>7235882</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>ACE Speakers Toastmasters</t>
+          <t>PoWerCommunicators Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>3</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13002,20 +13002,20 @@
       <c r="S120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U120" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V120" s="9" t="n">
-        <v>1</v>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13037,19 +13037,19 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2645756</v>
+        <v>28679751</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Aurora Toastmasters Club</t>
+          <t>Royal Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13063,17 +13063,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L121" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13101,20 +13101,20 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="10" t="n">
-        <v>5</v>
+      <c r="X121" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13136,19 +13136,19 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>7864607</v>
+        <v>28675608</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>ELIO Toastmasters Club</t>
+          <t>RSS Toastmasters Academy</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13162,17 +13162,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L122" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="8" t="n">
@@ -13188,23 +13188,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R122" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S122" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T122" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U122" s="10" t="n">
-        <v>3</v>
+      <c r="P122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
         <v>3</v>
@@ -13239,15 +13239,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>28679278</v>
+        <v>7335249</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Pearls of Expression Toastmasters Club</t>
+          <t>ACE Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13261,13 +13261,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
@@ -13299,20 +13299,20 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="10" t="n">
-        <v>4</v>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V123" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
@@ -13338,15 +13338,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>28679212</v>
+        <v>2645756</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Telfair Toastmasters Club</t>
+          <t>Aurora Toastmasters Club</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13360,17 +13360,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -13398,26 +13398,26 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U124" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -13433,19 +13433,19 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>28677974</v>
+        <v>7864607</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Axian Red Toastmasters Club</t>
+          <t>ELIO Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13459,25 +13459,25 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N125" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O125" s="7" t="inlineStr">
@@ -13485,32 +13485,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
+      <c r="P125" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q125" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R125" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S125" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U125" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13518,8 +13518,8 @@
       <c r="Z125" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA125" s="9" t="n">
-        <v>0</v>
+      <c r="AA125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB125" s="4" t="n"/>
       <c r="AC125" s="4" t="inlineStr"/>
@@ -13532,19 +13532,19 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>28677814</v>
+        <v>28679278</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Go BNI Toastmasters Club</t>
+          <t>Pearls of Expression Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13558,13 +13558,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -13602,14 +13602,14 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>0</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>3</v>
+      <c r="X126" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13631,19 +13631,19 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28676664</v>
+        <v>28679212</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Outstanding Toastmasters Club</t>
+          <t>Telfair Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13657,17 +13657,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13684,10 +13684,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13695,14 +13695,14 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U127" s="10" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13713,8 +13713,8 @@
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="10" t="n">
-        <v>1</v>
+      <c r="Z127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13734,15 +13734,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>7010199</v>
+        <v>28677974</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>The First Toastmasters Club of  Madagascar</t>
+          <t>Axian Red Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13756,67 +13756,67 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M128" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O128" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="M128" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N128" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O128" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P128" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z128" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA128" s="10" t="n">
-        <v>1</v>
+      <c r="AA128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB128" s="4" t="n"/>
       <c r="AC128" s="4" t="inlineStr"/>
@@ -13829,19 +13829,19 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28676459</v>
+        <v>28677814</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Airtel Madagascar Toastmasters Club</t>
+          <t>Go BNI Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13855,13 +13855,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13869,11 +13869,11 @@
         </is>
       </c>
       <c r="M129" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -13906,16 +13906,16 @@
         <v>0</v>
       </c>
       <c r="X129" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB129" s="4" t="n"/>
       <c r="AC129" s="4" t="inlineStr"/>
@@ -13928,19 +13928,19 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28677906</v>
+        <v>28676664</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Madacan Toastmasters Club</t>
+          <t>Outstanding Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13954,13 +13954,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13968,11 +13968,11 @@
         </is>
       </c>
       <c r="M130" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N130" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O130" s="7" t="inlineStr">
@@ -13984,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13992,29 +13992,29 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" s="9" t="n">
-        <v>0</v>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V130" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="9" t="n">
-        <v>0</v>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB130" s="4" t="n"/>
       <c r="AC130" s="4" t="inlineStr"/>
@@ -14027,19 +14027,19 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28676681</v>
+        <v>7010199</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Mirongo Toastmasters of Toamasina</t>
+          <t>The First Toastmasters Club of  Madagascar</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14053,17 +14053,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -14089,22 +14089,22 @@
         <v>0</v>
       </c>
       <c r="S131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="9" t="n">
-        <v>1</v>
+      <c r="V131" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -14130,15 +14130,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28679267</v>
+        <v>28676459</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Solitaire Toastmasters Club</t>
+          <t>Airtel Madagascar Toastmasters Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14152,25 +14152,25 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O132" s="7" t="inlineStr">
@@ -14196,23 +14196,23 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="10" t="n">
-        <v>4</v>
+      <c r="V132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X132" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="X132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" s="10" t="n">
-        <v>1</v>
+      <c r="Z132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="4" t="inlineStr"/>
@@ -14229,15 +14229,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28675645</v>
+        <v>28677906</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Tsingy Toastmasters Club</t>
+          <t>Madacan Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14251,25 +14251,25 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N133" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O133" s="7" t="inlineStr">
@@ -14278,40 +14278,40 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U133" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="10" t="n">
-        <v>7</v>
+      <c r="X133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB133" s="4" t="n"/>
       <c r="AC133" s="4" t="inlineStr"/>
@@ -14328,15 +14328,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28675795</v>
+        <v>28676681</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Young Challengers Toastmasters Club</t>
+          <t>Mirongo Toastmasters of Toamasina</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14350,17 +14350,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14377,31 +14377,31 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14415,8 +14415,305 @@
       <c r="AB134" s="4" t="n"/>
       <c r="AC134" s="4" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>28679267</v>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>Solitaire Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G135" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J135" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K135" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M135" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W135" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X135" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y135" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB135" s="4" t="n"/>
+      <c r="AC135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n">
+        <v>28675645</v>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Tsingy Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G136" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J136" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K136" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M136" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P136" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U136" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V136" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="4" t="n"/>
+      <c r="AC136" s="4" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>28675795</v>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Young Challengers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K137" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M137" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V137" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="4" t="n"/>
+      <c r="AC137" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC134"/>
+  <autoFilter ref="A1:AC137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14503,13 +14800,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
         <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -14536,13 +14833,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -14551,7 +14848,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -14569,7 +14866,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -14584,7 +14881,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -14617,7 +14914,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14635,13 +14932,13 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -14650,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -14668,7 +14965,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -14683,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -14701,13 +14998,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -14716,7 +15013,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -14734,7 +15031,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -14749,7 +15046,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -14767,7 +15064,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14782,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -14800,7 +15097,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14815,7 +15112,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14830,16 +15127,16 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -14848,7 +15145,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -14866,13 +15163,13 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -14881,7 +15178,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -14899,7 +15196,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14914,7 +15211,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -14932,7 +15229,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14947,7 +15244,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -14965,7 +15262,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14980,7 +15277,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -14998,7 +15295,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15013,7 +15310,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15031,7 +15328,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -15046,7 +15343,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -15064,7 +15361,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -15079,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -15097,7 +15394,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -15112,7 +15409,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -15145,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -15163,7 +15460,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -15178,7 +15475,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -15193,7 +15490,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
         <v>1</v>
@@ -15202,7 +15499,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -15211,7 +15508,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -15244,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -15262,7 +15559,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15277,7 +15574,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -15295,7 +15592,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -15310,7 +15607,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -15328,7 +15625,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15343,7 +15640,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -15361,7 +15658,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -15376,7 +15673,7 @@
         <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC137"/>
+  <dimension ref="A1:AC138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -990,13 +990,13 @@
         </is>
       </c>
       <c r="P3" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R3" s="9" t="n">
-        <v>1</v>
+      <c r="R3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S3" s="10" t="n">
         <v>3</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1094,8 +1094,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P4" s="9" t="n">
-        <v>3</v>
+      <c r="P4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q4" s="10" t="n">
         <v>2</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5" s="10" t="n">
         <v>7</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1415,8 +1415,8 @@
       <c r="S7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T7" s="9" t="n">
-        <v>0</v>
+      <c r="T7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U7" s="9" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1714,8 +1714,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P10" s="9" t="n">
-        <v>3</v>
+      <c r="P10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>1</v>
@@ -2415,13 +2415,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X18" s="10" t="n">
         <v>7</v>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3443,17 +3443,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -3490,8 +3490,8 @@
       <c r="V27" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>0</v>
+      <c r="W27" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X27" s="10" t="n">
         <v>7</v>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3802,8 +3802,8 @@
       <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="9" t="n">
-        <v>3</v>
+      <c r="V30" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4164,13 +4164,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4269,13 +4269,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4415,8 +4415,8 @@
       <c r="T36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U36" s="9" t="n">
-        <v>0</v>
+      <c r="U36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V36" s="10" t="n">
         <v>4</v>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4782,13 +4782,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4992,13 +4992,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5242,8 +5242,8 @@
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>3</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5347,8 +5347,8 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5820,13 +5820,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>58</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -6305,15 +6305,15 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>7229265</v>
+        <v>28681083</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Mount Meru</t>
+          <t>Mikocheni Toastmasters Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6354,31 +6354,31 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W55" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X55" s="10" t="n">
-        <v>7</v>
+      <c r="V55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y55" s="9" t="n">
         <v>0</v>
@@ -6389,32 +6389,30 @@
       <c r="AA55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB55" s="4" t="n">
-        <v>7</v>
-      </c>
+      <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>28679585</v>
+        <v>7229265</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Kasarani Toastmasters Club</t>
+          <t>Mount Meru</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6428,17 +6426,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6455,16 +6453,16 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q56" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q56" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="10" t="n">
         <v>1</v>
@@ -6472,14 +6470,14 @@
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W56" s="9" t="n">
-        <v>0</v>
+      <c r="V56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W56" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6491,13 +6489,9 @@
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC56" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="AC56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6511,15 +6505,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>28679879</v>
+        <v>28679585</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>LifeSMART Toastmasters Club</t>
+          <t>Kasarani Toastmasters Club</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6533,17 +6527,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6560,10 +6554,10 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q57" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R57" s="9" t="n">
         <v>0</v>
@@ -6571,20 +6565,20 @@
       <c r="S57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="9" t="n">
-        <v>0</v>
+      <c r="T57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>0</v>
+      <c r="X57" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6595,8 +6589,14 @@
       <c r="AA57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AB57" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6610,15 +6610,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>28679350</v>
+        <v>28679879</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Momentum Toastmasters Club</t>
+          <t>LifeSMART Toastmasters Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6632,17 +6632,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6688,15 +6688,13 @@
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB58" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB58" s="4" t="n"/>
       <c r="AC58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
@@ -6711,15 +6709,15 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>28678419</v>
+        <v>28679350</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Runda Elite Toastmasters Club</t>
+          <t>Momentum Toastmasters Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6733,17 +6731,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="J59" s="4" t="n">
-        <v>28</v>
-      </c>
       <c r="K59" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6759,17 +6757,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P59" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" s="10" t="n">
-        <v>2</v>
+      <c r="P59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -6777,32 +6775,28 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W59" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X59" s="10" t="n">
-        <v>7</v>
+      <c r="V59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="10" t="n">
-        <v>1</v>
+      <c r="Z59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC59" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6816,15 +6810,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1202269</v>
+        <v>28678419</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>SEMA</t>
+          <t>Runda Elite Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6838,13 +6832,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6864,17 +6858,17 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="9" t="n">
-        <v>1</v>
+      <c r="P60" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="9" t="n">
-        <v>1</v>
+      <c r="S60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T60" s="9" t="n">
         <v>0</v>
@@ -6886,7 +6880,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6901,11 +6895,11 @@
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC60" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -6917,19 +6911,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>28675568</v>
+        <v>1202269</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Bamburi Toastmasters Club</t>
+          <t>SEMA</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6943,25 +6937,25 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-10</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -6973,13 +6967,13 @@
         <v>0</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="9" t="n">
         <v>0</v>
@@ -6987,28 +6981,32 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="9" t="n">
-        <v>0</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W61" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X61" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7022,15 +7020,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>7946880</v>
+        <v>28675568</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Blue Eagles Toastmasters Club</t>
+          <t>Bamburi Toastmasters Club</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7044,25 +7042,25 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O62" s="7" t="inlineStr">
@@ -7071,49 +7069,45 @@
         </is>
       </c>
       <c r="P62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W62" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X62" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC62" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7127,15 +7121,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1197334</v>
+        <v>7946880</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Nairobi Toastmasters</t>
+          <t>Blue Eagles Toastmasters Club</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7149,13 +7143,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7176,7 +7170,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7185,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="10" t="n">
         <v>1</v>
@@ -7196,11 +7190,11 @@
       <c r="V63" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>1</v>
+      <c r="W63" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X63" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y63" s="9" t="n">
         <v>0</v>
@@ -7232,15 +7226,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>28680199</v>
+        <v>1197334</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Power Talk Toastmasters</t>
+          <t>Nairobi Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7254,13 +7248,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7281,7 +7275,7 @@
         </is>
       </c>
       <c r="P64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
         <v>0</v>
@@ -7290,19 +7284,19 @@
         <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>0</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -7310,16 +7304,20 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7333,15 +7331,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>6639074</v>
+        <v>28680199</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Rafiki Toastmasters</t>
+          <t>Power Talk Toastmasters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7355,17 +7353,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L65" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7382,10 +7380,10 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q65" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R65" s="9" t="n">
         <v>0</v>
@@ -7399,26 +7397,26 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="10" t="n">
-        <v>4</v>
+      <c r="V65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="10" t="n">
-        <v>1</v>
+      <c r="Z65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB65" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC65" s="4" t="inlineStr"/>
     </row>
@@ -7434,15 +7432,15 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>28680756</v>
+        <v>6639074</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Safaricom Toastmasters Club</t>
+          <t>Rafiki Toastmasters</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7456,17 +7454,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7483,10 +7481,10 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7500,14 +7498,14 @@
       <c r="U66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>0</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7518,7 +7516,9 @@
       <c r="AA66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB66" s="4" t="n"/>
+      <c r="AB66" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="AC66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
@@ -7529,15 +7529,15 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>28679092</v>
+        <v>28680756</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>MRM BS Toastmasters Club</t>
+          <t>Safaricom Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -7555,17 +7555,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7606,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7617,9 +7617,7 @@
       <c r="AA67" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB67" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
@@ -7634,15 +7632,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>5789341</v>
+        <v>28679092</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Nairobi Bottlers</t>
+          <t>MRM BS Toastmasters Club</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7656,17 +7654,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-16</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7683,10 +7681,10 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R68" s="9" t="n">
         <v>0</v>
@@ -7700,14 +7698,14 @@
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="10" t="n">
-        <v>4</v>
+      <c r="V68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -7719,13 +7717,9 @@
         <v>1</v>
       </c>
       <c r="AB68" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC68" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7739,15 +7733,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>28676279</v>
+        <v>5789341</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Strathmore University Toastmasters</t>
+          <t>Nairobi Bottlers</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7761,17 +7755,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L69" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7788,10 +7782,10 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q69" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>0</v>
@@ -7805,28 +7799,32 @@
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="9" t="n">
-        <v>0</v>
+      <c r="V69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X69" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7840,15 +7838,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5011794</v>
+        <v>28676279</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>TOASTMASTERS@CHIROMO</t>
+          <t>Strathmore University Toastmasters</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7862,13 +7860,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7889,49 +7887,45 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB70" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="Q70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA70" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7941,19 +7935,19 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>28677212</v>
+        <v>5011794</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Juja Toastmasters Club</t>
+          <t>TOASTMASTERS@CHIROMO</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7967,13 +7961,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7994,7 +7988,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>1</v>
@@ -8008,17 +8002,17 @@
       <c r="T71" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U71" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V71" s="10" t="n">
-        <v>4</v>
+      <c r="U71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8030,9 +8024,13 @@
         <v>1</v>
       </c>
       <c r="AB71" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8046,11 +8044,11 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>6613258</v>
+        <v>28677212</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Kilele Toastmasters Club</t>
+          <t>Juja Toastmasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -8068,13 +8066,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8104,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="10" t="n">
         <v>1</v>
@@ -8131,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AC72" s="4" t="inlineStr"/>
     </row>
@@ -8147,15 +8145,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>7474799</v>
+        <v>6613258</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Meru Toastmasters</t>
+          <t>Kilele Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8169,13 +8167,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8196,10 +8194,10 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q73" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
@@ -8207,32 +8205,32 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" s="9" t="n">
-        <v>3</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC73" s="4" t="inlineStr"/>
     </row>
@@ -8248,15 +8246,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>28680903</v>
+        <v>7474799</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Tatu City Toastmasters Club</t>
+          <t>Meru Toastmasters</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8270,17 +8268,17 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L74" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M74" s="8" t="n">
@@ -8315,24 +8313,26 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="9" t="n">
-        <v>0</v>
+      <c r="X74" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="10" t="n">
-        <v>1</v>
+      <c r="Z74" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB74" s="4" t="n"/>
+      <c r="AB74" s="4" t="n">
+        <v>5</v>
+      </c>
       <c r="AC74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
@@ -8347,15 +8347,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>6619736</v>
+        <v>28680903</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>The Thika Toastmasters</t>
+          <t>Tatu City Toastmasters Club</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8369,17 +8369,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8396,7 +8396,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>
@@ -8407,8 +8407,8 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="10" t="n">
-        <v>1</v>
+      <c r="T75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
@@ -8419,8 +8419,8 @@
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="10" t="n">
-        <v>7</v>
+      <c r="X75" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8431,14 +8431,8 @@
       <c r="AA75" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB75" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC75" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB75" s="4" t="n"/>
+      <c r="AC75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8448,15 +8442,15 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>28678445</v>
+        <v>6619736</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Chai Toastmasters Club</t>
+          <t>The Thika Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -8474,13 +8468,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8501,10 +8495,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="Q76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8512,14 +8506,14 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="9" t="n">
-        <v>0</v>
+      <c r="T76" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8537,9 +8531,13 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8553,11 +8551,11 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>5954085</v>
+        <v>28678445</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Eldoret Toastmasters</t>
+          <t>Chai Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -8575,10 +8573,10 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K77" s="4" t="n">
         <v>-4</v>
@@ -8602,10 +8600,10 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8613,8 +8611,8 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="10" t="n">
-        <v>1</v>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
@@ -8626,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8640,11 +8638,7 @@
       <c r="AB77" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+      <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8658,11 +8652,11 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>5553979</v>
+        <v>5954085</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Kisumu Toastmasters</t>
+          <t>Eldoret Toastmasters</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -8680,13 +8674,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8725,27 +8719,31 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X78" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y78" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA78" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB78" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8759,15 +8757,15 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>5913322</v>
+        <v>5553979</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Nakuru Toastmasters Club</t>
+          <t>Kisumu Toastmasters</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8781,13 +8779,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8808,31 +8806,31 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X79" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8844,31 +8842,31 @@
         <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>7846171</v>
+        <v>5913322</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>5 Speke Road Toastmasters</t>
+          <t>Nakuru Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8882,13 +8880,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8896,11 +8894,11 @@
         </is>
       </c>
       <c r="M80" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O80" s="7" t="inlineStr">
@@ -8909,10 +8907,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8920,32 +8918,32 @@
       <c r="S80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T80" s="9" t="n">
-        <v>0</v>
+      <c r="T80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="9" t="n">
-        <v>0</v>
+      <c r="V80" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="X80" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB80" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC80" s="4" t="inlineStr"/>
     </row>
@@ -8961,11 +8959,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>28676774</v>
+        <v>7846171</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Cente Toastmasters Club</t>
+          <t>5 Speke Road Toastmasters</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -8986,10 +8984,10 @@
         <v>0</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8997,11 +8995,11 @@
         </is>
       </c>
       <c r="M81" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O81" s="7" t="inlineStr">
@@ -9033,8 +9031,8 @@
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="10" t="n">
-        <v>4</v>
+      <c r="X81" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -9042,17 +9040,13 @@
       <c r="Z81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA81" s="10" t="n">
-        <v>1</v>
+      <c r="AA81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC81" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9066,11 +9060,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>28678857</v>
+        <v>28676774</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Ecobank Uganda Toastmasters Club</t>
+          <t>Cente Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -9091,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-8</v>
+        <v>-30</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9102,11 +9096,11 @@
         </is>
       </c>
       <c r="M82" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O82" s="7" t="inlineStr">
@@ -9138,8 +9132,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>0</v>
+      <c r="X82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9147,13 +9141,17 @@
       <c r="Z82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA82" s="9" t="n">
-        <v>0</v>
+      <c r="AA82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9167,15 +9165,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>28676023</v>
+        <v>28678857</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>High Tea Toastmasters Club</t>
+          <t>Ecobank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9189,17 +9187,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M83" s="8" t="n">
@@ -9233,26 +9231,26 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W83" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="X83" s="10" t="n">
-        <v>5</v>
+      <c r="V83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="10" t="n">
-        <v>1</v>
+      <c r="Z83" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC83" s="4" t="inlineStr"/>
     </row>
@@ -9268,15 +9266,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>7361841</v>
+        <v>28676023</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Kampala Sunrise Toastmasters</t>
+          <t>High Tea Toastmasters Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9290,13 +9288,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9304,11 +9302,11 @@
         </is>
       </c>
       <c r="M84" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O84" s="7" t="inlineStr">
@@ -9317,31 +9315,31 @@
         </is>
       </c>
       <c r="P84" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q84" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T84" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U84" s="10" t="n">
-        <v>2</v>
+      <c r="S84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V84" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9349,17 +9347,13 @@
       <c r="Z84" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA84" s="10" t="n">
-        <v>1</v>
+      <c r="AA84" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC84" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9373,15 +9367,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>3875767</v>
+        <v>7361841</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Kampala Toastmasters Club</t>
+          <t>Kampala Sunrise Toastmasters</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9395,17 +9389,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L85" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9422,28 +9416,28 @@
         </is>
       </c>
       <c r="P85" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="9" t="n">
-        <v>1</v>
+      <c r="S85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T85" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U85" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V85" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W85" s="9" t="n">
-        <v>2</v>
+      <c r="W85" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>7</v>
@@ -9474,19 +9468,19 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>28677335</v>
+        <v>3875767</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Absa Bank Uganda Toastmasters Club</t>
+          <t>Kampala Toastmasters Club</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9500,17 +9494,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9536,19 +9530,19 @@
         <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U86" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V86" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W86" s="10" t="n">
-        <v>7</v>
+      <c r="W86" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>7</v>
@@ -9563,11 +9557,11 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC86" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -9583,15 +9577,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7659827</v>
+        <v>28677335</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Entebbe Toastmasters Club</t>
+          <t>Absa Bank Uganda Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9605,13 +9599,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9632,28 +9626,28 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q87" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S87" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T87" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U87" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="S87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V87" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W87" s="9" t="n">
-        <v>1</v>
+      <c r="W87" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X87" s="10" t="n">
         <v>7</v>
@@ -9668,11 +9662,11 @@
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC87" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -9688,15 +9682,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>6892375</v>
+        <v>7659827</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Lubowa Toastmasters Club</t>
+          <t>Entebbe Toastmasters Club</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9710,17 +9704,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L88" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9736,29 +9730,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P88" s="10" t="n">
-        <v>5</v>
+      <c r="P88" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q88" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S88" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="9" t="n">
-        <v>1</v>
+      <c r="T88" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V88" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>7</v>
@@ -9793,15 +9787,15 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28678736</v>
+        <v>6892375</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>MU-JHU Toastmasters Club</t>
+          <t>Lubowa Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9818,10 +9812,10 @@
         <v>12</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9841,29 +9835,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P89" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q89" s="9" t="n">
-        <v>1</v>
+      <c r="P89" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S89" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" s="10" t="n">
-        <v>1</v>
+      <c r="S89" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T89" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="10" t="n">
-        <v>4</v>
+      <c r="V89" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9878,9 +9872,13 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -9894,15 +9892,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>7154422</v>
+        <v>28678736</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Muyenga Toastmasters Club</t>
+          <t>MU-JHU Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9916,13 +9914,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9943,10 +9941,10 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9960,14 +9958,14 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X90" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9979,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC90" s="4" t="inlineStr"/>
     </row>
@@ -9991,15 +9989,15 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>6633885</v>
+        <v>7154422</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Bukoto Toastmasters</t>
+          <t>Muyenga Toastmasters Club</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -10017,13 +10015,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10046,8 +10044,8 @@
       <c r="P91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" s="10" t="n">
-        <v>2</v>
+      <c r="Q91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10055,20 +10053,20 @@
       <c r="S91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U91" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" s="10" t="n">
-        <v>4</v>
+      <c r="T91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10080,13 +10078,9 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10100,15 +10094,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>8001305</v>
+        <v>6633885</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Kampala South Toastmasters Club</t>
+          <t>Bukoto Toastmasters</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10122,10 +10116,10 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>-11</v>
@@ -10149,7 +10143,7 @@
         </is>
       </c>
       <c r="P92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q92" s="10" t="n">
         <v>2</v>
@@ -10157,23 +10151,23 @@
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U92" s="10" t="n">
+      <c r="S92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10185,11 +10179,11 @@
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -10205,15 +10199,15 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>6924385</v>
+        <v>8001305</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Ntinda Toastmasters</t>
+          <t>Kampala South Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10227,13 +10221,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-17</v>
+        <v>-9</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10262,23 +10256,23 @@
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="9" t="n">
-        <v>1</v>
+      <c r="S93" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T93" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U93" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10290,11 +10284,11 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10310,15 +10304,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>28680290</v>
+        <v>6924385</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Pillar Toastmasters Club</t>
+          <t>Ntinda Toastmasters</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10332,17 +10326,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L94" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M94" s="8" t="n">
@@ -10359,31 +10353,31 @@
         </is>
       </c>
       <c r="P94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q94" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10395,9 +10389,13 @@
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC94" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10411,15 +10409,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>7955148</v>
+        <v>28680290</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>UNOC Toastmasters Club</t>
+          <t>Pillar Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10433,17 +10431,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10489,20 +10487,16 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB95" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC95" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10512,19 +10506,19 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>28679448</v>
+        <v>7955148</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Bugolobi Toastmasters Club</t>
+          <t>UNOC Toastmasters Club</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10538,13 +10532,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-8</v>
+        <v>-33</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10565,10 +10559,10 @@
         </is>
       </c>
       <c r="P96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="9" t="n">
         <v>0</v>
@@ -10576,36 +10570,36 @@
       <c r="S96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="10" t="n">
-        <v>1</v>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="10" t="n">
-        <v>4</v>
+      <c r="V96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="10" t="n">
-        <v>1</v>
+      <c r="Z96" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC96" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -10621,15 +10615,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>28680326</v>
+        <v>28679448</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Executives</t>
+          <t>Bugolobi Toastmasters Club</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10643,17 +10637,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10670,10 +10664,10 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9" t="n">
         <v>0</v>
@@ -10681,34 +10675,38 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X97" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC97" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10722,15 +10720,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28675508</v>
+        <v>28680326</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Exceed Toastmasters</t>
+          <t>Bujumbura Executives</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10744,17 +10742,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L98" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10770,50 +10768,46 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P98" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q98" s="10" t="n">
-        <v>2</v>
+      <c r="P98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T98" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U98" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T98" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="10" t="n">
-        <v>6</v>
+      <c r="X98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="10" t="n">
-        <v>1</v>
+      <c r="Z98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC98" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -10827,15 +10821,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>28675532</v>
+        <v>28675508</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Mbarara Toastmasters Club</t>
+          <t>Exceed Toastmasters</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10849,13 +10843,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10875,26 +10869,26 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P99" s="9" t="n">
-        <v>1</v>
+      <c r="P99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q99" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R99" s="10" t="n">
+      <c r="R99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="S99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="V99" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10916,7 +10910,7 @@
       </c>
       <c r="AC99" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -10932,15 +10926,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>28679445</v>
+        <v>28675532</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Red Sea</t>
+          <t>Mbarara Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10954,17 +10948,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10981,13 +10975,13 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q100" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S100" s="9" t="n">
         <v>0</v>
@@ -10999,25 +10993,31 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="9" t="n">
-        <v>0</v>
+      <c r="X100" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB100" s="4" t="n"/>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AB100" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11031,11 +11031,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>28677104</v>
+        <v>28679445</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>UBL Toastmasters Club</t>
+          <t>Red Sea</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -11053,17 +11053,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="8" t="n">
@@ -11103,8 +11103,8 @@
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="10" t="n">
-        <v>5</v>
+      <c r="X101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11115,14 +11115,8 @@
       <c r="AA101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB101" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC101" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB101" s="4" t="n"/>
+      <c r="AC101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11132,15 +11126,15 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>28679460</v>
+        <v>28677104</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>AIMS RIC</t>
+          <t>UBL Toastmasters Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11158,13 +11152,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11208,8 +11202,8 @@
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>0</v>
+      <c r="X102" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11221,9 +11215,13 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11237,15 +11235,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28676457</v>
+        <v>28679460</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Bujumbura Bilingual</t>
+          <t>AIMS RIC</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11259,13 +11257,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-9</v>
+        <v>-20</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11286,7 +11284,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11295,22 +11293,22 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T103" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>5</v>
+      <c r="X103" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11322,7 +11320,7 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC103" s="4" t="inlineStr"/>
     </row>
@@ -11338,15 +11336,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28676690</v>
+        <v>28676457</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Elevated Speakers Toastmasters Club</t>
+          <t>Bujumbura Bilingual</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11360,13 +11358,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11387,31 +11385,31 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S104" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
@@ -11423,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AC104" s="4" t="inlineStr"/>
     </row>
@@ -11439,15 +11437,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>7692944</v>
+        <v>28676690</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Kigali Bilingual Toastmasters Club</t>
+          <t>Elevated Speakers Toastmasters Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11461,13 +11459,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11488,7 +11486,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>1</v>
@@ -11497,7 +11495,7 @@
         <v>0</v>
       </c>
       <c r="S105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T105" s="9" t="n">
         <v>0</v>
@@ -11505,32 +11503,28 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="10" t="n">
-        <v>4</v>
+      <c r="V105" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X105" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="10" t="n">
-        <v>1</v>
+      <c r="Z105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC105" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11544,15 +11538,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>5233390</v>
+        <v>7692944</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Techy Talkers Toastmasters Club</t>
+          <t>Kigali Bilingual Toastmasters Club</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11566,17 +11560,17 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L106" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M106" s="8" t="n">
@@ -11593,16 +11587,16 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="9" t="n">
         <v>0</v>
@@ -11613,8 +11607,8 @@
       <c r="V106" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W106" s="9" t="n">
-        <v>3</v>
+      <c r="W106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X106" s="10" t="n">
         <v>7</v>
@@ -11629,11 +11623,11 @@
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC106" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -11649,15 +11643,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>5251769</v>
+        <v>5233390</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>TRES Toastmasters Club</t>
+          <t>Techy Talkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11671,17 +11665,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L107" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11697,29 +11691,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P107" s="10" t="n">
-        <v>5</v>
+      <c r="P107" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="T107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V107" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W107" s="10" t="n">
-        <v>8</v>
+      <c r="W107" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>7</v>
@@ -11734,35 +11728,35 @@
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC107" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28677895</v>
+        <v>5251769</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Imperium Toastmasters Club</t>
+          <t>TRES Toastmasters Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11776,17 +11770,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11802,29 +11796,29 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P108" s="9" t="n">
-        <v>0</v>
+      <c r="P108" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W108" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -11838,8 +11832,14 @@
       <c r="AA108" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB108" s="4" t="n"/>
-      <c r="AC108" s="4" t="inlineStr"/>
+      <c r="AB108" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11853,11 +11853,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>7863227</v>
+        <v>28677895</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Mauritius Revenue Authority</t>
+          <t>Imperium Toastmasters Club</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11875,13 +11875,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
@@ -11920,13 +11920,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X109" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11952,11 +11952,11 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28675654</v>
+        <v>7863227</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>NBA Toastmasters Club</t>
+          <t>Mauritius Revenue Authority</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11974,17 +11974,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L110" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M110" s="8" t="n">
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -12019,13 +12019,13 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X110" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12051,11 +12051,11 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28681044</v>
+        <v>28675654</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Ocorian NewGen Toastmasters Club</t>
+          <t>NBA Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -12073,17 +12073,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12100,7 +12100,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12123,8 +12123,8 @@
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>0</v>
+      <c r="X111" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
@@ -12150,11 +12150,11 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>28681048</v>
+        <v>28681044</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Ocorian NexGen Toastmasters Club</t>
+          <t>Ocorian NewGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -12249,11 +12249,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2558</v>
+        <v>28681048</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Port Louis Toastmasters Club</t>
+          <t>Ocorian NexGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12271,13 +12271,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12298,16 +12298,16 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -12316,13 +12316,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="10" t="n">
-        <v>5</v>
+      <c r="X113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12344,19 +12344,19 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28675649</v>
+        <v>2558</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Bagatelle Toastmasters Club</t>
+          <t>Port Louis Toastmasters Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12370,13 +12370,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12397,16 +12397,16 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T114" s="9" t="n">
         <v>0</v>
@@ -12414,14 +12414,14 @@
       <c r="U114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W114" s="10" t="n">
-        <v>9</v>
+      <c r="V114" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W114" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12447,11 +12447,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>1226180</v>
+        <v>28675649</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Financial Toastmasters Club</t>
+          <t>Bagatelle Toastmasters Club</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12469,13 +12469,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12505,19 +12505,19 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W115" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>7</v>
@@ -12546,15 +12546,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>28680744</v>
+        <v>1226180</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>IQ-EQ Mauritius Toastmasters Club</t>
+          <t>Financial Toastmasters Club</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12568,13 +12568,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -12604,22 +12604,22 @@
         <v>0</v>
       </c>
       <c r="S116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U116" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>0</v>
+      <c r="X116" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
@@ -12645,15 +12645,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>592015</v>
+        <v>28680744</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Plateau Toastmasters Club</t>
+          <t>IQ-EQ Mauritius Toastmasters Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12667,17 +12667,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12705,20 +12705,20 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V117" s="10" t="n">
-        <v>4</v>
+      <c r="T117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X117" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12744,15 +12744,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>28679140</v>
+        <v>592015</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Standard Bank (Mauritius) Limited</t>
+          <t>Plateau Toastmasters Club</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12766,17 +12766,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12804,20 +12804,20 @@
       <c r="S118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V118" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W118" s="10" t="n">
-        <v>6</v>
+      <c r="W118" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12839,19 +12839,19 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>5438132</v>
+        <v>28679140</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>NewGen Toastmasters Club</t>
+          <t>Standard Bank (Mauritius) Limited</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12865,17 +12865,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L119" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -12909,14 +12909,14 @@
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
+      <c r="V119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W119" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12942,15 +12942,15 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>7235882</v>
+        <v>5438132</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>PoWerCommunicators Toastmasters Club</t>
+          <t>NewGen Toastmasters Club</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12964,17 +12964,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13008,14 +13008,14 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="10" t="n">
-        <v>4</v>
+      <c r="V120" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X120" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -13041,15 +13041,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28679751</v>
+        <v>7235882</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Royal Toastmasters Club</t>
+          <t>PoWerCommunicators Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13063,17 +13063,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L121" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="8" t="n">
@@ -13090,10 +13090,10 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13107,14 +13107,14 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>2</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X121" s="9" t="n">
-        <v>1</v>
+      <c r="X121" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
@@ -13140,11 +13140,11 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>28675608</v>
+        <v>28679751</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>RSS Toastmasters Academy</t>
+          <t>Royal Toastmasters Club</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -13162,13 +13162,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13207,13 +13207,13 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X122" s="10" t="n">
-        <v>7</v>
+      <c r="X122" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -13235,19 +13235,19 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>7335249</v>
+        <v>28675608</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>ACE Speakers Toastmasters</t>
+          <t>RSS Toastmasters Academy</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13261,17 +13261,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L123" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="8" t="n">
@@ -13288,7 +13288,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -13299,14 +13299,14 @@
       <c r="S123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V123" s="9" t="n">
-        <v>1</v>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13338,15 +13338,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>2645756</v>
+        <v>7335249</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Aurora Toastmasters Club</t>
+          <t>ACE Speakers Toastmasters</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13360,13 +13360,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>4</v>
+        <v>-11</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -13404,14 +13404,14 @@
       <c r="U124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V124" s="10" t="n">
-        <v>4</v>
+      <c r="V124" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
@@ -13437,15 +13437,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>7864607</v>
+        <v>2645756</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>ELIO Toastmasters Club</t>
+          <t>Aurora Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13459,13 +13459,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13485,32 +13485,32 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P125" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q125" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R125" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S125" s="10" t="n">
-        <v>3</v>
+      <c r="P125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T125" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U125" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V125" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13536,15 +13536,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>28679278</v>
+        <v>7864607</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Pearls of Expression Toastmasters Club</t>
+          <t>ELIO Toastmasters Club</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13558,17 +13558,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L126" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13584,23 +13584,23 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P126" s="9" t="n">
+      <c r="P126" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q126" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R126" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S126" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" s="9" t="n">
-        <v>0</v>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U126" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="V126" s="10" t="n">
         <v>4</v>
@@ -13609,7 +13609,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13635,15 +13635,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28679212</v>
+        <v>28679278</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Telfair Toastmasters Club</t>
+          <t>Pearls of Expression Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13657,13 +13657,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -13701,20 +13701,20 @@
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="9" t="n">
-        <v>0</v>
+      <c r="V127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
@@ -13730,15 +13730,15 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28677974</v>
+        <v>28679212</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Axian Red Toastmasters Club</t>
+          <t>Telfair Toastmasters Club</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13756,13 +13756,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13770,11 +13770,11 @@
         </is>
       </c>
       <c r="M128" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N128" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O128" s="7" t="inlineStr">
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q128" s="9" t="n">
         <v>0</v>
@@ -13807,16 +13807,16 @@
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB128" s="4" t="n"/>
       <c r="AC128" s="4" t="inlineStr"/>
@@ -13833,15 +13833,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>28677814</v>
+        <v>28677974</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Go BNI Toastmasters Club</t>
+          <t>Axian Red Toastmasters Club</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13855,13 +13855,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13869,11 +13869,11 @@
         </is>
       </c>
       <c r="M129" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N129" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O129" s="7" t="inlineStr">
@@ -13905,8 +13905,8 @@
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>3</v>
+      <c r="X129" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -13914,8 +13914,8 @@
       <c r="Z129" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA129" s="10" t="n">
-        <v>1</v>
+      <c r="AA129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB129" s="4" t="n"/>
       <c r="AC129" s="4" t="inlineStr"/>
@@ -13932,15 +13932,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28676664</v>
+        <v>28677814</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Outstanding Toastmasters Club</t>
+          <t>Go BNI Toastmasters Club</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -13957,10 +13957,10 @@
         <v>14</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -13992,20 +13992,20 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V130" s="10" t="n">
-        <v>4</v>
+      <c r="T130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W130" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X130" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X130" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14031,15 +14031,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>7010199</v>
+        <v>28676664</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>The First Toastmasters Club of  Madagascar</t>
+          <t>Outstanding Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14053,17 +14053,17 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M131" s="8" t="n">
@@ -14080,31 +14080,31 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U131" s="9" t="n">
-        <v>0</v>
+      <c r="U131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V131" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W131" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X131" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -14126,19 +14126,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>28676459</v>
+        <v>7010199</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Airtel Madagascar Toastmasters Club</t>
+          <t>The First Toastmasters Club of  Madagascar</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14152,25 +14152,25 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="K132" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N132" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O132" s="7" t="inlineStr">
@@ -14179,7 +14179,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14188,31 +14188,31 @@
         <v>0</v>
       </c>
       <c r="S132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>0</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="X132" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB132" s="4" t="n"/>
       <c r="AC132" s="4" t="inlineStr"/>
@@ -14229,11 +14229,11 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28677906</v>
+        <v>28676459</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Madacan Toastmasters Club</t>
+          <t>Airtel Madagascar Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
@@ -14328,15 +14328,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28676681</v>
+        <v>28677906</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Mirongo Toastmasters of Toamasina</t>
+          <t>Madacan Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14350,13 +14350,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14364,11 +14364,11 @@
         </is>
       </c>
       <c r="M134" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O134" s="7" t="inlineStr">
@@ -14395,22 +14395,22 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X134" s="10" t="n">
-        <v>5</v>
+      <c r="X134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
+      <c r="Z134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB134" s="4" t="n"/>
       <c r="AC134" s="4" t="inlineStr"/>
@@ -14427,15 +14427,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>28679267</v>
+        <v>28676681</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Solitaire Toastmasters Club</t>
+          <t>Mirongo Toastmasters of Toamasina</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14449,17 +14449,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14493,14 +14493,14 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W135" s="10" t="n">
-        <v>4</v>
+      <c r="V135" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14526,11 +14526,11 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>28675645</v>
+        <v>28679267</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Tsingy Toastmasters Club</t>
+          <t>Solitaire Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -14548,17 +14548,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L136" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14575,31 +14575,31 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U136" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V136" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
@@ -14625,11 +14625,11 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28675795</v>
+        <v>28675645</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Young Challengers Toastmasters Club</t>
+          <t>Tsingy Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
@@ -14647,13 +14647,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>1</v>
@@ -14712,8 +14712,107 @@
       <c r="AB137" s="4" t="n"/>
       <c r="AC137" s="4" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>28675795</v>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Young Challengers Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="J138" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K138" s="4" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M138" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U138" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V138" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="4" t="n"/>
+      <c r="AC138" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC137"/>
+  <autoFilter ref="A1:AC138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14800,7 +14899,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -14833,7 +14932,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -14965,13 +15064,13 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -14980,7 +15079,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -14998,7 +15097,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -15064,7 +15163,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15097,7 +15196,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15127,16 +15226,16 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -15145,7 +15244,7 @@
         <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -15163,7 +15262,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -15196,7 +15295,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15262,13 +15361,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -15361,7 +15460,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -15427,7 +15526,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -15460,7 +15559,7 @@
         <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -15559,7 +15658,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/114/inyear.xlsx
+++ b/docs/d/114/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 26 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 26 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="U3" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" s="9" t="n">
         <v>3</v>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" s="10" t="n">
         <v>7</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1583,13 +1583,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>7</v>
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2456,8 +2456,8 @@
       <c r="T17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U17" s="9" t="n">
-        <v>0</v>
+      <c r="U17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>2</v>
@@ -2502,7 +2502,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2548,8 +2548,8 @@
       <c r="Q18" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R18" s="9" t="n">
-        <v>1</v>
+      <c r="R18" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="S18" s="10" t="n">
         <v>2</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="P30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>1</v>
@@ -3859,13 +3859,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L34" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>75</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="P36" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="10" t="n">
         <v>2</v>
@@ -4422,7 +4422,7 @@
         <v>4</v>
       </c>
       <c r="W36" s="10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="X36" s="10" t="n">
         <v>7</v>
@@ -4580,13 +4580,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -5198,13 +5198,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5404,13 +5404,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>7</v>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6832,13 +6832,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6864,8 +6864,8 @@
       <c r="Q60" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R60" s="9" t="n">
-        <v>0</v>
+      <c r="R60" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S60" s="10" t="n">
         <v>2</v>
@@ -6937,13 +6937,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>1</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7397,11 +7397,11 @@
       <c r="U65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="9" t="n">
-        <v>0</v>
+      <c r="V65" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W65" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X65" s="10" t="n">
         <v>7</v>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8066,17 +8066,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L72" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8095,8 +8095,8 @@
       <c r="P72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q72" s="9" t="n">
-        <v>1</v>
+      <c r="Q72" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
@@ -8114,7 +8114,7 @@
         <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>7</v>
@@ -8167,13 +8167,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8200,16 +8200,16 @@
         <v>2</v>
       </c>
       <c r="R73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U73" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73" s="10" t="n">
         <v>4</v>
@@ -8573,13 +8573,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8880,13 +8880,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>4</v>
       </c>
       <c r="W80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X80" s="10" t="n">
         <v>6</v>
@@ -9288,13 +9288,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>0</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>4</v>
       </c>
       <c r="W84" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>5</v>
@@ -9422,7 +9422,7 @@
         <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S85" s="10" t="n">
         <v>2</v>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>0</v>
@@ -9809,13 +9809,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>2</v>
       </c>
       <c r="R89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S89" s="10" t="n">
         <v>2</v>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9914,13 +9914,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -10326,13 +10326,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-17</v>
+        <v>-15</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10532,17 +10532,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="L96" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-11</v>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10984,7 +10984,7 @@
         <v>2</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="9" t="n">
         <v>0</v>
@@ -11459,13 +11459,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11770,17 +11770,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11818,7 +11818,7 @@
         <v>4</v>
       </c>
       <c r="W108" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X108" s="10" t="n">
         <v>7</v>
@@ -12496,7 +12496,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T115" s="9" t="n">
         <v>0</v>
@@ -12964,13 +12964,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9" t="n">
         <v>0</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13089,8 +13089,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P121" s="9" t="n">
-        <v>3</v>
+      <c r="P121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>1</v>
@@ -13643,7 +13643,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13683,8 +13683,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P127" s="9" t="n">
-        <v>3</v>
+      <c r="P127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q127" s="9" t="n">
         <v>0</v>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14152,13 +14152,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14178,8 +14178,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P132" s="9" t="n">
-        <v>3</v>
+      <c r="P132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14199,8 +14199,8 @@
       <c r="V132" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W132" s="9" t="n">
-        <v>3</v>
+      <c r="W132" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X132" s="10" t="n">
         <v>6</v>
@@ -14746,13 +14746,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -15112,7 +15112,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -15262,7 +15262,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -15295,7 +15295,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15361,13 +15361,13 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -15376,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -15508,7 +15508,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -15574,7 +15574,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -15658,7 +15658,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15691,7 +15691,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -15724,13 +15724,13 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
